--- a/src/main/resources/common-templates/templates/age-rating-template.xlsx
+++ b/src/main/resources/common-templates/templates/age-rating-template.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -123,6 +123,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,7 +491,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.005" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -506,13 +509,11 @@
       <c r="C1" s="4" t="n"/>
       <c r="D1" s="4" t="n"/>
       <c r="E1" s="4" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
       <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="3" t="n"/>
@@ -520,22 +521,27 @@
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="3" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="6" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
       <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -566,10 +572,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="J2:R2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/common-templates/templates/age-rating-template.xlsx
+++ b/src/main/resources/common-templates/templates/age-rating-template.xlsx
@@ -39,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -106,11 +106,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -125,6 +126,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,7 +502,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.005" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -504,71 +515,190 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="3" t="n"/>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="5" t="n"/>
-      <c r="J1" s="6" t="n"/>
+      <c r="A1" s="7" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="9" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="8" t="n"/>
+      <c r="M1" s="8" t="n"/>
+      <c r="N1" s="8" t="n"/>
+      <c r="O1" s="8" t="n"/>
+      <c r="P1" s="8" t="n"/>
+      <c r="Q1" s="8" t="n"/>
+      <c r="R1" s="8" t="n"/>
+      <c r="S1" s="8" t="n"/>
+      <c r="T1" s="8" t="n"/>
+      <c r="U1" s="8" t="n"/>
+      <c r="V1" s="8" t="n"/>
+      <c r="W1" s="8" t="n"/>
+      <c r="X1" s="8" t="n"/>
+      <c r="Y1" s="8" t="n"/>
+      <c r="Z1" s="8" t="n"/>
+      <c r="AA1" s="8" t="n"/>
+      <c r="AB1" s="8" t="n"/>
+      <c r="AC1" s="8" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="6" t="n"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
+      <c r="N2" s="8" t="n"/>
+      <c r="O2" s="8" t="n"/>
+      <c r="P2" s="8" t="n"/>
+      <c r="Q2" s="8" t="n"/>
+      <c r="R2" s="8" t="n"/>
+      <c r="S2" s="8" t="n"/>
+      <c r="T2" s="8" t="n"/>
+      <c r="U2" s="8" t="n"/>
+      <c r="V2" s="8" t="n"/>
+      <c r="W2" s="8" t="n"/>
+      <c r="X2" s="8" t="n"/>
+      <c r="Y2" s="8" t="n"/>
+      <c r="Z2" s="8" t="n"/>
+      <c r="AA2" s="8" t="n"/>
+      <c r="AB2" s="8" t="n"/>
+      <c r="AC2" s="8" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="M3" s="6" t="n"/>
-      <c r="N3" s="6" t="n"/>
-      <c r="P3" s="6" t="n"/>
-      <c r="Q3" s="6" t="n"/>
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="9" t="n"/>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="9" t="n"/>
+      <c r="Q3" s="9" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="8" t="n"/>
+      <c r="T3" s="8" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="8" t="n"/>
+      <c r="W3" s="8" t="n"/>
+      <c r="X3" s="8" t="n"/>
+      <c r="Y3" s="8" t="n"/>
+      <c r="Z3" s="8" t="n"/>
+      <c r="AA3" s="8" t="n"/>
+      <c r="AB3" s="8" t="n"/>
+      <c r="AC3" s="8" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="n"/>
+      <c r="P4" s="8" t="n"/>
+      <c r="Q4" s="8" t="n"/>
+      <c r="R4" s="8" t="n"/>
+      <c r="S4" s="8" t="n"/>
+      <c r="T4" s="8" t="n"/>
+      <c r="U4" s="8" t="n"/>
+      <c r="V4" s="8" t="n"/>
+      <c r="W4" s="8" t="n"/>
+      <c r="X4" s="8" t="n"/>
+      <c r="Y4" s="8" t="n"/>
+      <c r="Z4" s="8" t="n"/>
+      <c r="AA4" s="8" t="n"/>
+      <c r="AB4" s="8" t="n"/>
+      <c r="AC4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n"/>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n"/>
+      <c r="T5" s="8" t="n"/>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="8" t="n"/>
+      <c r="W5" s="8" t="n"/>
+      <c r="X5" s="8" t="n"/>
+      <c r="Y5" s="8" t="n"/>
+      <c r="Z5" s="8" t="n"/>
+      <c r="AA5" s="8" t="n"/>
+      <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="8" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
